--- a/docs/downloads/11/tbl_saisonnalite_alaotra_tous.xlsx
+++ b/docs/downloads/11/tbl_saisonnalite_alaotra_tous.xlsx
@@ -384,7 +384,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -405,7 +405,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -426,7 +426,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -447,7 +447,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -468,7 +468,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -489,7 +489,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -510,7 +510,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -531,7 +531,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -552,7 +552,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -573,7 +573,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -594,7 +594,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -615,7 +615,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -636,7 +636,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -657,7 +657,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -678,7 +678,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -699,7 +699,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -720,7 +720,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -741,7 +741,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -762,7 +762,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -783,7 +783,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -804,7 +804,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -825,7 +825,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -846,7 +846,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -867,7 +867,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -888,7 +888,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -909,7 +909,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -930,7 +930,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -951,7 +951,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -972,7 +972,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -993,7 +993,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1014,7 +1014,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1035,7 +1035,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1056,7 +1056,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1077,7 +1077,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1098,7 +1098,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1119,7 +1119,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1140,7 +1140,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1161,7 +1161,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1182,7 +1182,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1203,7 +1203,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1224,7 +1224,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1245,7 +1245,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1266,7 +1266,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1287,7 +1287,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1308,7 +1308,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1329,7 +1329,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1350,7 +1350,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1371,7 +1371,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
